--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260918.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260918.xlsx
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>87,353,663</t>
+          <t>44,780,400</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>44,780,400</t>
+          <t>87,353,663</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,238,000</t>
+          <t>18,084,381</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>18,084,381</t>
+          <t>7,238,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
